--- a/legasus/backend/data/products.xlsx
+++ b/legasus/backend/data/products.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -425,18 +425,21 @@
         <v>images</v>
       </c>
       <c r="I1" t="str">
+        <v>sizeChartImage</v>
+      </c>
+      <c r="J1" t="str">
         <v>quantity</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>stockStatus</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>badge</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>createdAt</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>source</v>
       </c>
     </row>
@@ -465,19 +468,22 @@
       <c r="H2" t="str">
         <v>["data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAZwAAABOCAYAAAAUwKCpAAAAAXNSR0IArs4c6QAAAARnQU1BAACxjwv8YQUAAAAJcEhZcwAADsMAAA7DAcdvqGQAABkESURBVHhe7d15eFNV3sDx783WPW0p+44gyCYgoAIqsiiCDI6IzihuoIOijKiv8AqIOo5KBxfUcRlcsO7jDI7CK4oyqKAgiKBWLKvshULp3jRNmtz7/pHmJrlN2pQWaOvv8zx50nvO79ymt3nuL+fcc08Ul9utEURRlMCGZtg21utlxpKAcPHVqW28EEKI08vtKufiEZcG5QJj3gBNA5OmheQbQrbDnPuN8b4yY0lAuPjqaJpW6zZCCCFOL3+yCZy+q57HTYRJCsHbWphGxnghhBCCCKNU/pRhChRETiLV1flVFxJNeyGEEI1bcO8mkHh8hYqihA6pRfoZpWrSMG4LIYQQ/gTjTxHBPR6TEu5CTSVj0qlJdTmotgmqtvFCCCFOHy3MJLNQGkp5uauyvxMoDm5U+1lrwV2pUJHKI6ltvKg/WmEhpXdMw/vrrwDYxo0n/qG/GMPwfLeR0v+5G9xuYxUApg4dSVz8Kqa0NKiowLX0X5S/mYGWnw+AkpxMzHXXE3PtZJSYmJC2Fd98jWPWvaCqAFjOPY+EhU+hxMXpMVpREc7nnsH9+UrfazCZsPTpS9z9czF37ebbz9drcMy+D1QVJclO4vMvojRvQem0qajZ2QDE3flnYm68GQDvtizK0h/Hu3OHr01cHLbLxxM7fQZKYqL+u0+WX/ceYs/+bFzuClq1aEb/Pt2xWi3GsEZt956DZGbtpn3blpx7Tm9jtWhkjLPUAslH05OLokS4hhPp52h6OVEGiQZOq3CjOcoCBR5PcLVOczgiJhsAKipA9YLHQ9nCdJzPPK0nGyoTRvlLL+BcuMAXG8S7LUtPNgDq/n1oxcX6tlZSguP+Wbg/Xh54DaqKJ/MnSqdPw/Nzpq/M4w3sR1PBqwae/fuq/Ps8P2dSOnMG3u3b9Daa04lr6b9xzLoXraREb1PfDmTnsOCZDB5e+DJffvM9W37axmtvL+PO2X9j5er1xvBGLWvnXn7etpu/v/I+JaVB7zPRiNU8KmWeN++BhxVFQUFBC+qd1KWXU13HxBhbndrENiVHc/M5mJ3D8bzCqB8FhSU0S7XX2zHTyhy4ly9DKy0FwNy1G9aRo4xhqPv2UvHfVcZinZKYhG3CFagHDlD+4t8jJif14CEsgwZhat3aV+Dx4Hr/n6gH9geCvF6sQ4dhatMWAPfyj3B/sDRQH8zlQsvLw3rxSNSDB/XXqNhs2MZejpKQEPL3WQYNxtyrN870x1Ere3VG6tGjmFq3xtKzl7Gqzg5k57BgUQYd27fm7tuv5Yqxwxk+bCDjx1xIfHwcb/3rE1RVpVePM4xN68zj8fLRJ1/x1r8+4Z2lK1m38Sfi42N5d+lnvPH+Cv771UZ+3ZdNh3atSEqMNzY/IT26dWL40HNY8fk6WjZvhrO8vMp7OtwjNiaGGJvVuDtxmnm9HjLeeAtFUcIMrQV6OIrTWa6FVAb/GCHpGK/7VD3J1c+wWm1im5IHF/yDvQcOG4urZTaZ+Muc2+nUvvKEXUdq7jFKb52KmnMEANullxH/18eMYVR8+QWO+2fp2/Hz5mMZMlTfVmJjUZLsVPx3FY559+tlCU88DbGxOO65Sz/pBw9raQX5lN4+De++vfq+AOLum03M1X8AoGz+PN9QGmA+szuJz71A+ZsZuN57BwBT6zYkvroE79at+mtUEhNJfO5FlJYtQv6+2NumY/vdhJCymGsnE3vjzZTedSfeXTuhmuNQVwueySDZnsgdUycZqwDYkrmdRS+9y9x7ptCzexdjdZ2sXL2eD/7vC0ZeOJju3TqStWMvq77aSLcuHRgz8nwKCotZ++0PmEwmHp073di8ThYsep2snaH/4+pcMXY4kyZU/eAjTi+3q5wRIy8FjNdyAkNqhLsPJ6qfDV2nqhf4IyeKqrGRab/Rm0AfmXM7b730SK0eGS88XG/Jpi6UJDumFi31h5JkB8Ab3FOxWFASEjG1aYOSmKQX+4e1qOxNqHl5+rafNyvLWBSgKJjatsXUurXv0aIFmMzGqNqJjcXUvoO+TyU52RhRZ7/uPUTWjj1c9buRxirdOWefxfmD+rJ2/Q/Gqjr7ZsOPXHB+f669agwD+/XkhmvGcf/Mm5h7z82cN7APl40ayrQbJ7L/4BEOZh81Nq+TLp3b0bdXtyrvZ+PjzRf/QmyMjc4d2hh3IRqsqufuKtdwjL2XE/VbTBSidkxpzUlc8gb2jz/F/vGnxPzxOr1OPXQIrcR3vcYy+FyUhARf+cEDvutGgLlXYGjLu2snZU8txPa7CdiXrcC+bAWJr77um6wQJcWejKlDB33b9cG/qfj8MxIW/E3fZ9x9s0Pa1Ic9+33DVa1aNDNWhejTsys79xwwFtdZTm4+/fp0Dynr1eMMLJbARIXOHduQmBDHkaPHQ+Lqqlvn9uzec9BYXMX+gzmUu9ycVc+9O3Fqhb8PJyhXREocxl5OVZETV6R9Cp83/rmCx55eUqtH+rNvcDyv0LirU85x/ywKzxtI8RXjUXOPGat1mupFLSjwTSgIw7P5e/1nS69e+sw076GDqDk5AFhHjsbUqZMeV7Hqc0pvnVplGC5aSkwMMVdNApvNV+B2U/a3xylLfwzNefIubLvcFcTGVP7OasTF2HC7QydW1Ie01GTy84uMxSG8Xi+lDidpqfXbw+vapT3Ochc5x6r2ZoNt27mXNq2ak5gQmKEoGp8qQ2p+0Zb5VVcnaqdVy2b07N6lVo/uXTsad9OgacePUzr1JorHj9Ufrn++66tzOgNJw2LB1PVMlLTmvrqiItTDhwAwtWpFwkOPoKQGegbe3bsoveVmKtZ8pZfVhvXikcTeehuYKjv/qor7ow8pve1PqEfrdzjJr1WLZhzOqbnncPDwMVq3jL7HFq22bVrwy449xuIQmVm7AWjftqWxqk5SU+wkJcbz6z7f/zSSbbv20qNb4MOFaBxCr+UEDan51WZoraYkU1O9CO+ykUOYOH5ErR/N01KMu2qUtOJi1GzfCUhJSsLcuQumlq18laqKd/t2Pdbcuw9Jr2Vg7nGWXqaVluJ4YA4V69fpZVFTFGJvvImEx9ND7rnx7tiOY+aMsNeV6qp/n+6oqsrqtZuMVTp3hYe1325hYP+exqo6u+C8fmz6IYvsI7nGKt3S5asZ1L8nMVH0xGqrx5md+fHnHWzbuTfiY9evBzire2djU9FghT/360Nq1SWHsMNuVDtqVqnGANHEJKQ/QcrGzdiXfYypReRPw0pCAtaLR6DEVZ1mq2YfQivyDfEo8fEoaWm+CQCVvDt2hNwXZGrXjsRXlvhmr/l7Jm43rowlaGUnMBSmKFhHjCLpzXdDEpl37x7cyz4MCa0PVquFieNHkPHe/7ElM5BM/dwVHv7+ynvYrFYuGznEWF1nA/v1pEe3Trzw2r9wuapOW1/26RoO5xzn+mvGGavqxeiLziXzl908vuj1iI/UFDsDzw78L0TDVE0aAUBxOMr0adFhp0EH5Yxwccb7cqpOZa77FOlo45qKxjwtOiH9Cawjqs62Kl/yKuWLXwKqn5ocO/VWXP9+H+eTCw17CDB37kLiP17G9Z//4F7uSwCWfv2Jm/cg5a8sxvXWGwCYmjcncfGreHftimpadMzV1+B4YC5q5XBe7K3TsF44PHAjKGC9cDgJ6Qsh6IJ6fVm6fDXLPl3D+YP60qdnV2JjbBw6fIy1327BZrORc/Q4UydfwYgLBhqb1llRcSl/ffJV2rZuwczb/ojZ7Jvdt/67TP6R8QF33nI15w3sY2wmBARNi9ZCVhjw/exLQhqghF7Dqa6XEyzaOHFi7rz1GubeM6V2j3un0rFd5bBTA2TuGDT+7vGgOUrRCgvDXoyvduozoObl+aZNV04gUHNy8GzfhlZSEn5WWmysniC08nLUgnwoc6K5XXqIYrGgudyoBw8E9rl1K8TEoCQFpm6fTJMmjGLuPVOwmM0sX7mWt//9Kdt37WPs6GE88fBdXDtxDK+/u5wvv9lsbFpnyfZE5twzhdy8Ah5KX8zB7KO8+f4KXnnrQ+6YenKTjdtdwYJnMph27+N8sip0GHT12u+Yfl86jzz5KkXFvvu1ROOlOBxlGmF6L/7naFYfMF7vMfZIInVQjHGRRBsn6o+xhxNOQvoTUDkzLRJTu3YkvrwENfsQjpl/DiQYm8336cdVedK3WEh4chGW3n0onTEd7w7f0JKSlOSbEu3xoubn6cvNJDyWjlqQH9ITUuLi0Vzleoy5V28Sn3sBzeWi9I5pqPsr7wUy/G4lLp6EZ/+O+ayeOGbdi2fjBl+cyYQSF6dPwwaIvWkKsXfM0LdPtU/+u473PviM+ffdelImirgrKnjz/RWsWbeF1i3TuGvaH+lwkj/IrF67ic+/3MCEsReR8d7HvLJonl5399ynmDD2Ir7e8CMD+vZgwmUXhbQVDUOkHk5giKyyh2Ps3RifjcmkPkXbU9J+ozeANgmV65ZZevXGOiroDnG3O5BsAOvwi7EOGoyam4t6LDAbLH7eg9iXrSDp7XdDekmerF+wjhyNuUtgqRfNWRZYM81mI/a661GSkjA1b47t8gkh13dCfveoUVh69fZNi/7jdYFp0aoakmxMHTpi+/2V+vbpMG70MKZPnUS7NoFrWvXJZrVy6/W/55H7b+Ovc6ef9GQD0LJFKodzclnx+boqQ8Id2rVi5epv2b3nYI33KYmGr8ostepEmjwgyaAJUkxgjuLtYTEHTuThmE2+fVmtxM2eQ+xNN4es9ozNRsykq4mf/xBYraiHgyYMJCSg+CcLxMahNAud/qwkJpLw/ItYh18c8hqUZs2In/cg1tGX6GWxN95E/EOPhOwDm42YaycTN3sOWH3rc1mHDiPx6WdD7u/BZMLcuzcJTz6NqW27QPlpMnTw2STEn9z7Ubp0ahfVvUH1oW/PbsyacQMXDzuHe++YHFI387ZruXTE+dx9+3UndVhPnBpKaamjyqQB49BZbYfVqg6B1X3iALWMFQ2Yqvpu+gRMqanVJ6xoVVSgFhWhxNj05XTC0jTftSNVrfF3a2VlaI5SFHtyla9OEEIERDukppSWOqq9hqOf5IPO9VXqDAnHWOfbDtnUGeOqU5tYIYQQp0Zowgmu8ecK35TpyB/vhBBCiHpU46QB43Ow2lzHqaleCCFE02aKdjUA45CZEEIIURsnNKQWtrdSYz4KHxB2XxHUJlYIIUTDckIrDQSL1CZSuRBCiN+myh5OaO8jUgIybgshhBDRCvkCtkiiiRFCCCGqY/J3bqJJKsETB8LFhyuLxom2E0II0XhUmTQgJ38hhBAnQ1DCCX8dx7htLA8RfiKaEEIIETpLLZzq6vwixRjLjdtCCCF+O5TiklIt8K2dvkU2jWulGZ/9PZmQtdT8MdWuqVb3RTyjjTvdVFWSqxANjcnUOM4fjU20a6kpRcUlmqIolYkidFVoY6KJJuHU9JXTkfKFMS6SaONOt8KiEmOREOI0irFZiYuLNRaLenCCCScQLAlHCCFENKJNOPqkgXDXV8KVBQtbL/lACCFEGFWmRUcjbKIRQgghqnFCCUcIIYSoraAvgvc9heu9RHUPTgTGNsZtv0jlQgghmoZG18PRNE2SkxBCNEIRb/wMV+ZnvNdGCCGEqEmYHs6JJZPqEpQQQggR1dcTCCGEEHUV0sM5NcnnxHpQQgghGrcwQ2pCCCFE/asx4dTU66mpXgghhCCahHMiJAkJIYQwCptwwiWMcGVCCCFEtJTComLfatH+FaGDvqbAuEp0cJlm+CqD4OeTvWI0tYz9LfF4PBQWlZCSnISimCgoLCIuLpYYm5WCwmI0TQUgISEBAKeznNSUZBwOB15VJSXZ3iSPraPMidNZTkqKnZKSUmw2GxazmeKSUlJT7JjNZgqLijGbTNjtSQAUF/u+YsJuT9Lb+49VucsFgMlkxp6URHFJSchxticlEhNjC3kNDZXH4wl5zcHbgH6MXO4KHA4HAIpiIjXFjsViweVyU1RcTLLdrrf3vwe9XlVvX1bmDHvcVNVLQkICCfFx+msqLi5p0u/HpqZeVosWjU/W9t2cP+JKFi95j3UbvmfA0MvJeHspWdt3M2TkRAYMHc+AoePJeHspGW8vZeCw8Wz+4WfmP7qIP915P2XOcuMum4Q132xk+Jg/kPnzNqZOn036Uy+yes16Lp1wAwcOHeZ/56fTZ/AYeg68hBdfeQtN05j/6CLGTpzCr3v3c8fd8xk3cQp5+fnMf3SRfhzHTZzC7j17GDdxCvfMfoTMrdsZMnIia9d9Z3wJDdKRnGOMunwy/YeMo//Qy9matVN/rzzzwhLWrvuOISMnkrV9NxlvL9X/bn8ZwBvvfMCAoeNZ8dmXUPkeHHvlzWRu3c68vzzJ9JnzcLkrIh63AUPH073fCBa/9i6aprH4tXfpOfAS+gwew5yHnsDj9RpetWiswg6picbv+cVvMmve46iqr0cDkJqSzKcfZpC9awN3TrsBAI/Xy9frNwW1bJo6d2yHyWRiz94DZB8+yr4D2WzfsZvOndqTX1DEso9X8fLzC5h19zTefu8jjucVALBv/yFuu2seq79aF7K/SVeOI3vXBr5b8xHN05oBsPnHrWQfPhoS19BtzdpJQWERy95/hY7t27Dmm4163dfrN1FU2cvzG3LuAHb+9CW7M7/i7D5noWkamVu3oygKP/y0NST2l207+eTzL5l60x/03ku44/bai39jxm038sY7H3Dg0BFWffE1d/zpBp5Of4Av1qwnP9/3vxCNX60TjvSEGr5kexKdO7bD6SzHarXq5aqqkl9QqA8V+X259lsKCopCypqa1q1a0DwtlW82bCa/oJBDh46waXMm7dq0xmqx4FVVbFYrVqsVj9erDz12O6MTubl5tG/bOmR/Tmc5ucfz8Xg8elnO0Vw2bf4pJK6ha5aajKPMyfqNm3lnybPcfP0kvW5r1k627fD1Yvxc7gpyc/NwudwAFBeXsnf/QS4cOpht23fjKHMC4Ha7eenVdxhwdm9GXjREbx/uuJlMJhITfUO8NpuVli2b8+mqr+jXtyef/Od10pr5EpNo/GqdcETDZzKZmHHbjTz+8CxatkjTy4uKS5g89W7mP7pILzuza2dUVa1yYmlq7PYkzuzamRWffkFqSjLH8wrYtCWTs/ucVe01gv5n9+KpBfO48ooxIeUrVn4RMqwEcOmoC/ls9dpG9aHsnP59eGD2DJ545mXmPvwEauXwVWpKMgP79wnp8QBs+XErw0ZP0ocMjx3Po6i4hAuGDubAoSMcz8uHymtm+w9kh7QlwnGbcvss0p96ieuv/T2tWzZn/v/+GXtSIuMn3cJPP2dhNstpqqmQ/2QT1aF9W84d1C+kzD+k9uzCB/Wy5mmpDOjXm8NHGtdQUG1ZzGa6ntGJMqeTvr170KF9G5zOcrp17WwMDaUojB5xAYmVkyz8Jl05Th9W8hty7jm43RWUl/sujDcGbncFvxs3mrdefZqv12/izfc+1OvGjL6IXbv2hsT7h9QuGXkBALt+3UdZmZP2bVvjdJZz4OBhAMwmExMuH833WzL5ZdtOvX244/bQnJm0bNGcdm18vcjY2BgyFj/JuEsvZu7DT5BzNFePFY3byUk4kT8witPIP6R2LPe4PvQBcMGQQdV+ym8q+lae5Pr37UX7tq1JSbbToX2bytllNo7kHCM3N4+E+DgsFouxeQins5xjucc5nleA1+sbfmvTuiV9evcwhjZo6zZsZtioq3CUOenQrg05R4/pdWd268IZXTqGxPuH1PzDYj9v3U5efiGPpD9HYVEx2yp7LnZ7EpOvuYIzu3XhP8s/03t9kY9bd776egNlTie3z3yAxxY+T/+ze1NaWkZJqW9mnGj8Tk7CEQ2Sf0jNP0vNr3ev7pxZ0yf9JqBzx3YkJsTT86xudD2jEy1bpJHWLIUundpz3TVXMOehhbz+9lJuuekamqWmGJuHWLHyC322VUFhIVR+Mh8z6kJjaIM2+Jy+DB54NtNmzKHU4WDyNb/X69KapXDB0EEh8f4htSEjJ/Jj5ja2btvJ1VeOY+Oajxh7yXAyt27Xk4vdnsTYSy9m5ao1HMw+AtUct/MHD2D9xs2UlDi4afJVfPTxKub/9SluvG4iXTp3CHkNovHS78PBf59NDffh+J+rvQ+H0O/MMX56jvRh2hhXndrECiGEOHlqfR9OKF9QY7r4KYQQomGLkHCEEEKI+lWHhCNDWkIIIaJXJeFEO4xWl3QT7e8QQgjRdFRJOEIIIcTJIAlHCCHEKSEJRwghxClhQq6pCCGEOAWkhyOEEOKUkIQjhBDilJCEI4QQ4pSQhCOEEOKUUAqLijUqF8NUFAU0/8+VAdUs4um/+7NKOdUv3ulfHNQoXFkktYk9HTybvzcWiRpYBoauTCyEaByiXbxTEs5JUnjeQGORqIb55luwTrnFWCxEvTGZTNhsga9cF/Un6oSTfeRohITjmyqtoOh7qJJYJOFE5N2y2VgkatJ/gLFEiHplNslVhJNC8zBmzPiaE470cIQQQtRFtD0cSfdCCCFOCUk4Qggh6iTaASdJOEIIIU6J/wedgR/KlirmcQAAAABJRU5ErkJggg=="]</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2">
         <v>19</v>
       </c>
-      <c r="J2" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K2" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L2" t="str">
         <v>Admin Upload</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>1774155617711</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>upload</v>
       </c>
     </row>
@@ -506,19 +512,22 @@
       <c r="H3" t="str">
         <v>["https://images.unsplash.com/photo-1515886657613-9f3515b0c78f?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1507679799987-c73779587ccf?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1500648767791-00dcc994a43e?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1506629905607-d9c381e87b1d?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1483985988355-763728e1935b?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1521572267360-ee0c2909d518?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3">
         <v>34</v>
       </c>
-      <c r="J3" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K3" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L3" t="str">
         <v>Graphic Drop</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>1773312315000</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>catalog</v>
       </c>
     </row>
@@ -547,19 +556,22 @@
       <c r="H4" t="str">
         <v>["https://images.unsplash.com/photo-1521119989659-a83eee488004?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1504593811423-6dd665756598?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1503342217505-b0a15ec3261c?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1506629905607-d9c381e87b1d?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1483985988355-763728e1935b?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1521572267360-ee0c2909d518?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4">
         <v>2</v>
       </c>
-      <c r="J4" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K4" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L4" t="str">
         <v>Linen Blend</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>1773139515001</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
         <v>catalog</v>
       </c>
     </row>
@@ -588,19 +600,22 @@
       <c r="H5" t="str">
         <v>["https://images.unsplash.com/photo-1523398002811-999ca8dec234?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1500648767791-00dcc994a43e?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1507679799987-c73779587ccf?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1483985988355-763728e1935b?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1503342217505-b0a15ec3261c?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1521572267360-ee0c2909d518?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5">
         <v>21</v>
       </c>
-      <c r="J5" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K5" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L5" t="str">
         <v>Utility</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>1773053115001</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
         <v>catalog</v>
       </c>
     </row>
@@ -629,19 +644,22 @@
       <c r="H6" t="str">
         <v>["https://images.unsplash.com/photo-1523398002811-999ca8dec234?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1500648767791-00dcc994a43e?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1507679799987-c73779587ccf?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1483985988355-763728e1935b?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1503342217505-b0a15ec3261c?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1521572267360-ee0c2909d518?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6">
         <v>8</v>
       </c>
-      <c r="J6" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K6" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L6" t="str">
         <v>Classic Fit</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>1772966715001</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
         <v>catalog</v>
       </c>
     </row>
@@ -670,19 +688,22 @@
       <c r="H7" t="str">
         <v>["https://images.unsplash.com/photo-1523398002811-999ca8dec234?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1500648767791-00dcc994a43e?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1507679799987-c73779587ccf?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1483985988355-763728e1935b?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1503342217505-b0a15ec3261c?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1521572267360-ee0c2909d518?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7">
         <v>14</v>
       </c>
-      <c r="J7" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K7" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L7" t="str">
         <v>Bootcut Fit</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>1772880315001</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
         <v>catalog</v>
       </c>
     </row>
@@ -711,19 +732,22 @@
       <c r="H8" t="str">
         <v>["https://images.unsplash.com/photo-1521119989659-a83eee488004?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1504593811423-6dd665756598?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1503342217505-b0a15ec3261c?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1506629905607-d9c381e87b1d?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1483985988355-763728e1935b?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1521572267360-ee0c2909d518?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8">
         <v>5</v>
       </c>
-      <c r="J8" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K8" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L8" t="str">
         <v>Oversized Fit</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>1772793915001</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
         <v>catalog</v>
       </c>
     </row>
@@ -752,19 +776,22 @@
       <c r="H9" t="str">
         <v>["https://images.unsplash.com/photo-1515886657613-9f3515b0c78f?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1507679799987-c73779587ccf?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1500648767791-00dcc994a43e?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1506629905607-d9c381e87b1d?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1483985988355-763728e1935b?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1521572267360-ee0c2909d518?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9">
         <v>30</v>
       </c>
-      <c r="J9" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K9" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L9" t="str">
         <v>Soft Cotton</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>1772707515001</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
         <v>catalog</v>
       </c>
     </row>
@@ -793,19 +820,22 @@
       <c r="H10" t="str">
         <v>["https://images.unsplash.com/photo-1521119989659-a83eee488004?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1504593811423-6dd665756598?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1503342217505-b0a15ec3261c?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1506629905607-d9c381e87b1d?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1483985988355-763728e1935b?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1521572267360-ee0c2909d518?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10">
         <v>12</v>
       </c>
-      <c r="J10" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K10" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L10" t="str">
         <v>Relaxed Fit</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>1772621115001</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
         <v>catalog</v>
       </c>
     </row>
@@ -834,19 +864,22 @@
       <c r="H11" t="str">
         <v>["https://images.unsplash.com/photo-1521119989659-a83eee488004?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1504593811423-6dd665756598?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1503342217505-b0a15ec3261c?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1506629905607-d9c381e87b1d?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1483985988355-763728e1935b?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1521572267360-ee0c2909d518?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11">
         <v>12</v>
       </c>
-      <c r="J11" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K11" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L11" t="str">
         <v>Linen Blend</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>1772534715001</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
         <v>catalog</v>
       </c>
     </row>
@@ -875,19 +908,22 @@
       <c r="H12" t="str">
         <v>["https://images.unsplash.com/photo-1515886657613-9f3515b0c78f?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1507679799987-c73779587ccf?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1500648767791-00dcc994a43e?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1506629905607-d9c381e87b1d?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1483985988355-763728e1935b?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1521572267360-ee0c2909d518?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12">
         <v>12</v>
       </c>
-      <c r="J12" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K12" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L12" t="str">
         <v>Soft Drop</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>1772448315001</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
         <v>catalog</v>
       </c>
     </row>
@@ -916,19 +952,22 @@
       <c r="H13" t="str">
         <v>["https://images.unsplash.com/photo-1496747611176-843222e1e57c?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1524504388940-b1c1722653e1?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1512436991641-6745cdb1723f?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1515886657613-9f3515b0c78f?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1483985988355-763728e1935b?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1521572267360-ee0c2909d518?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13">
         <v>12</v>
       </c>
-      <c r="J13" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K13" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L13" t="str">
         <v>Fresh Drop</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>1772361915001</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
         <v>catalog</v>
       </c>
     </row>
@@ -957,19 +996,22 @@
       <c r="H14" t="str">
         <v>["https://images.unsplash.com/photo-1542291026-7eec264c27ff?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1549298916-b41d501d3772?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1525966222134-fcfa99b8ae77?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1600185365483-26d7a4cc7519?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1595950653106-6c9ebd614d3a?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1560769629-975ec94e6a86?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14">
         <v>12</v>
       </c>
-      <c r="J14" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K14" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L14" t="str">
         <v>New Sole</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>1772275515001</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
         <v>catalog</v>
       </c>
     </row>
@@ -998,25 +1040,28 @@
       <c r="H15" t="str">
         <v>["https://images.unsplash.com/photo-1542291026-7eec264c27ff?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1549298916-b41d501d3772?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1525966222134-fcfa99b8ae77?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1600185365483-26d7a4cc7519?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1595950653106-6c9ebd614d3a?auto=format&amp;fit=crop&amp;w=1200&amp;q=80","https://images.unsplash.com/photo-1560769629-975ec94e6a86?auto=format&amp;fit=crop&amp;w=1200&amp;q=80"]</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15">
         <v>12</v>
       </c>
-      <c r="J15" t="str">
-        <v>in-stock</v>
-      </c>
       <c r="K15" t="str">
+        <v>in-stock</v>
+      </c>
+      <c r="L15" t="str">
         <v>New Sole</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>1772189115001</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
         <v>catalog</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N15"/>
   </ignoredErrors>
 </worksheet>
 </file>